--- a/BeatnotePostHotCellF1=4/Jul16,2026/Fit_ResultJul16.xlsx
+++ b/BeatnotePostHotCellF1=4/Jul16,2026/Fit_ResultJul16.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jul16,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCellF1=4\Jul16,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE56DC5-2AA0-45D9-9FFC-D126011E6745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E74248B-E0B2-4092-A301-A71AE12A8873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -177,19 +177,13 @@
   </si>
   <si>
     <t>Jul16,2026+12-55-34PM</t>
-  </si>
-  <si>
-    <t>Jul16,2026+2-16-32PM</t>
-  </si>
-  <si>
-    <t>Jul16,2026+2-51-44PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,9 +555,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:V36"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,7 +592,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="42.75">
+    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -631,7 +625,7 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="42.75">
+    <row r="3" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -658,7 +652,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="42.75">
+    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -683,7 +677,7 @@
       <c r="H4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="42.75">
+    <row r="5" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -708,7 +702,7 @@
       <c r="H5" s="1"/>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="42.75">
+    <row r="6" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -733,7 +727,7 @@
       <c r="H6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:22" ht="42.75">
+    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -758,7 +752,7 @@
       <c r="H7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="42.75">
+    <row r="8" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -783,7 +777,7 @@
       <c r="H8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:22" ht="42.75">
+    <row r="9" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -808,7 +802,7 @@
       <c r="H9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:22" ht="42.75">
+    <row r="10" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -833,7 +827,7 @@
       <c r="H10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:22" ht="42.75">
+    <row r="11" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -858,7 +852,7 @@
       <c r="H11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:22" ht="42.75">
+    <row r="12" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -883,7 +877,7 @@
       <c r="H12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="42.75">
+    <row r="13" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -908,7 +902,7 @@
       <c r="H13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:22" ht="42.75">
+    <row r="14" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -933,7 +927,7 @@
       <c r="H14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:22" ht="42.75">
+    <row r="15" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -958,7 +952,7 @@
       <c r="H15" s="1"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:22" ht="42.75">
+    <row r="16" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -983,7 +977,7 @@
       <c r="H16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="1:20" ht="42.75">
+    <row r="17" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -1008,7 +1002,7 @@
       <c r="H17" s="1"/>
       <c r="T17" s="1"/>
     </row>
-    <row r="18" spans="1:20" ht="42.75">
+    <row r="18" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -1033,7 +1027,7 @@
       <c r="H18" s="1"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="1:20" ht="42.75">
+    <row r="19" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -1057,7 +1051,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:20" ht="42.75">
+    <row r="20" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -1081,7 +1075,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:20" ht="42.75">
+    <row r="21" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -1105,7 +1099,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:20" ht="42.75">
+    <row r="22" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1129,7 +1123,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:20" ht="42.75">
+    <row r="23" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -1153,7 +1147,7 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:20" ht="42.75">
+    <row r="24" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1177,7 +1171,7 @@
       </c>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:20" ht="42.75">
+    <row r="25" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1201,7 +1195,7 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:20" ht="42.75">
+    <row r="26" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -1225,7 +1219,7 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:20" ht="42.75">
+    <row r="27" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -1249,7 +1243,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:20" ht="42.75">
+    <row r="28" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -1273,7 +1267,7 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:20" ht="42.75">
+    <row r="29" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -1297,7 +1291,7 @@
       </c>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:20" ht="42.75">
+    <row r="30" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -1321,7 +1315,7 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:20" ht="42.75">
+    <row r="31" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -1345,7 +1339,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:20" ht="42.75">
+    <row r="32" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -1369,7 +1363,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="42.75">
+    <row r="33" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
@@ -1393,7 +1387,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" ht="42.75">
+    <row r="34" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -1417,7 +1411,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" ht="42.75">
+    <row r="35" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
@@ -1441,7 +1435,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" ht="42.75">
+    <row r="36" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
@@ -1472,13 +1466,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
-  <dimension ref="A1:T38"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:T39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1514,977 +1508,1075 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="42.75">
+    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6.4664938143317294E-2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1.6246517474351401</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1.2832394093051001E-3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>-4.5039025450265098E-5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2.5839166631620101</v>
+      </c>
+      <c r="G2" s="1">
+        <v>39.641874099198702</v>
+      </c>
+      <c r="H2" s="1">
+        <v>9.7140132624605404E-4</v>
+      </c>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6.48925563524336E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1.62375786770658</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.3305457179744299E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-4.00517488312179E-5</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2.8349694907848599</v>
+      </c>
+      <c r="G3" s="1">
+        <v>40.593764138579402</v>
+      </c>
+      <c r="H3" s="1">
+        <v>7.5220762972069005E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1">
+        <v>6.4717624366303003E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1.62445657349427</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.1488949262361599E-3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-1.3036912286815E-5</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2.58429248620671</v>
+      </c>
+      <c r="G4" s="1">
+        <v>39.655885072180403</v>
+      </c>
+      <c r="H4" s="1">
+        <v>9.1684713323811199E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1">
+        <v>6.5096945322289101E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.62388373467633</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.3211340143322401E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-3.4790584613092498E-5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2.8359477332004999</v>
+      </c>
+      <c r="G5" s="1">
+        <v>40.647063324229002</v>
+      </c>
+      <c r="H5" s="1">
+        <v>7.5220619099783804E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1">
+        <v>6.4780635694392893E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.62447539983621</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.1619972120418399E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-6.8861837271727797E-6</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2.8335126302115099</v>
+      </c>
+      <c r="G6" s="1">
+        <v>39.823144021208201</v>
+      </c>
+      <c r="H6" s="1">
+        <v>7.7087511549222599E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6.4828747039054904E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.6240658175753799</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.34611239648697E-3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-3.8973982051738203E-5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.83370514136926</v>
+      </c>
+      <c r="G7" s="1">
+        <v>39.988258402110297</v>
+      </c>
+      <c r="H7" s="1">
+        <v>9.1953865341760596E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6.4845896931015903E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.62401974426023</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.0979108637087199E-3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.4089692879704E-6</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2.5840868643469199</v>
+      </c>
+      <c r="G8" s="1">
+        <v>39.864498854738699</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7.7565063008285797E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6.4898532838035997E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.62396843192504</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.1956276763198401E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-1.26144128146059E-5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2.5864852467241501</v>
+      </c>
+      <c r="G9" s="1">
+        <v>39.834025351401003</v>
+      </c>
+      <c r="H9" s="1">
+        <v>5.7909850528746704E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.4393394651674596E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.62350084108952</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.1208199841096799E-3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1.15713154860445E-5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2.5874975079645299</v>
+      </c>
+      <c r="G10" s="1">
+        <v>39.7938634010386</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6.5174494399200295E-4</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+    </row>
+    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1">
+        <v>6.4836933722996301E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1.6239805242455601</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.19211779373671E-3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-1.47392572695851E-5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2.7952427936491899</v>
+      </c>
+      <c r="G11" s="1">
+        <v>39.9063412006278</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6.1029898590043996E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1">
+        <v>6.4898123293677099E-2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1.62446194859036</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.5153340410589096E-4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2.2974559750219399E-5</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2.5857738595170998</v>
+      </c>
+      <c r="G12" s="1">
+        <v>39.8921995023534</v>
+      </c>
+      <c r="H12" s="1">
+        <v>6.10804171042956E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1">
+        <v>6.48141939607636E-2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1.62430809318148</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1.0035122222886101E-3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>4.0243907751170497E-5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.5843366232105698</v>
+      </c>
+      <c r="G13" s="1">
+        <v>40.848044370866901</v>
+      </c>
+      <c r="H13" s="1">
+        <v>7.5220782687832803E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1">
+        <v>6.4945690313312696E-2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1.62477629876114</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1.1116336638491301E-3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-9.9613128905330105E-6</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2.5851745878824302</v>
+      </c>
+      <c r="G14" s="1">
+        <v>40.431274550485</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6.3322102843056498E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1">
+        <v>6.4750632359324503E-2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.62486422735943</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1.0427331838012901E-3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>8.9550238829479297E-6</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2.5839485123600898</v>
+      </c>
+      <c r="G15" s="1">
+        <v>40.171612651024198</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5.94867040280642E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1">
+        <v>6.46466961945657E-2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.62564222201577</v>
+      </c>
+      <c r="D16" s="1">
+        <v>8.1502383110239297E-4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4.0838120759855502E-5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2.5848191834529199</v>
+      </c>
+      <c r="G16" s="1">
+        <v>40.1711464486228</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5.8204235675425901E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1">
+        <v>6.5070391277710998E-2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1.62496427111479</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1.2154222328969E-3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>-2.2617714945597699E-5</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2.5850757544900298</v>
+      </c>
+      <c r="G17" s="1">
+        <v>40.9412162645243</v>
+      </c>
+      <c r="H17" s="1">
+        <v>7.52210521137962E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1">
+        <v>6.5003508402351404E-2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1.6252221813656</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1.00142273410833E-3</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.6165173725499801E-5</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2.5846415023185201</v>
+      </c>
+      <c r="G18" s="1">
+        <v>40.022290198391502</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5.80588460945622E-4</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+    </row>
+    <row r="19" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1">
+        <v>6.4702157939462199E-2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.6248694903974701</v>
+      </c>
+      <c r="D19" s="1">
+        <v>6.2295334582414101E-4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>6.6553208117818997E-5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2.58376117360344</v>
+      </c>
+      <c r="G19" s="1">
+        <v>40.064650740782099</v>
+      </c>
+      <c r="H19" s="1">
+        <v>9.2297928858573104E-4</v>
+      </c>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+    </row>
+    <row r="20" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6.4789520162763903E-2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.62534447696757</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1.0570390030800801E-3</v>
+      </c>
+      <c r="E20" s="2">
+        <v>-3.4741554776058601E-6</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2.3337676178968501</v>
+      </c>
+      <c r="G20" s="1">
+        <v>39.959290575140301</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9.64805681173401E-4</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+    </row>
+    <row r="21" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1">
+        <v>6.4698100702121605E-2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1.6246767088488201</v>
+      </c>
+      <c r="D21" s="1">
+        <v>9.6775230495947499E-4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.2811293098655901E-5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2.5856907920489398</v>
+      </c>
+      <c r="G21" s="1">
+        <v>39.9546538394614</v>
+      </c>
+      <c r="H21" s="1">
+        <v>6.0286949917879099E-4</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="22" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1">
+        <v>6.39060983563466E-2</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1.62117967101831</v>
+      </c>
+      <c r="D22" s="1">
+        <v>7.4081403150172604E-4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>5.6192417281096199E-5</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2.5845061978561699</v>
+      </c>
+      <c r="G22" s="1">
+        <v>39.995168329571896</v>
+      </c>
+      <c r="H22" s="1">
+        <v>6.5377103435253702E-4</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+    </row>
+    <row r="23" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1">
+        <v>6.4217223623450101E-2</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1.62085950749531</v>
+      </c>
+      <c r="D23" s="1">
+        <v>7.4047369634396498E-4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>4.5377426729487801E-5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>2.58470374765621</v>
+      </c>
+      <c r="G23" s="1">
+        <v>41.021264876333198</v>
+      </c>
+      <c r="H23" s="1">
+        <v>7.5220673259059599E-4</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+    </row>
+    <row r="24" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="1">
+        <v>6.4146735969449406E-2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1.6207551046439601</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4.5136333774447901E-4</v>
+      </c>
+      <c r="E24" s="2">
+        <v>9.1475583453467195E-5</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2.5836871191877</v>
+      </c>
+      <c r="G24" s="1">
+        <v>40.149907567450903</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5.9932628140443097E-4</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+    </row>
+    <row r="25" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="1">
+        <v>6.4629796704458606E-2</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1.62037111978291</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9.3384052361766595E-4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1.56159530632519E-5</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2.3343853002852901</v>
+      </c>
+      <c r="G25" s="1">
+        <v>40.203188349951198</v>
+      </c>
+      <c r="H25" s="1">
+        <v>8.9170930421049802E-4</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+    </row>
+    <row r="26" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="1">
+        <v>6.43943878164248E-2</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1.6201546919669101</v>
+      </c>
+      <c r="D26" s="1">
+        <v>9.0910924833357903E-4</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1.70131664205842E-5</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2.3345264481158301</v>
+      </c>
+      <c r="G26" s="1">
+        <v>41.231840194538897</v>
+      </c>
+      <c r="H26" s="1">
+        <v>7.5221060694970502E-4</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+    </row>
+    <row r="27" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1">
-        <v>8.2788867848109599E-2</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B27" s="1">
+        <v>6.4478725052475205E-2</v>
+      </c>
+      <c r="C27" s="1">
         <v>1.6201064661050599</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D27" s="1">
         <v>7.9009458966678402E-4</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E27" s="2">
         <v>3.7883289781573801E-5</v>
       </c>
-      <c r="F2" s="1">
-        <v>2.3966518061659001</v>
-      </c>
-      <c r="G2" s="1">
-        <v>40.358092384738598</v>
-      </c>
-      <c r="H2" s="1">
-        <v>6.4313486507170997E-4</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="42.75">
-      <c r="A3" s="1" t="s">
+      <c r="F27" s="1">
+        <v>2.3354650842921698</v>
+      </c>
+      <c r="G27" s="1">
+        <v>40.302753317946198</v>
+      </c>
+      <c r="H27" s="1">
+        <v>6.1090985848738901E-4</v>
+      </c>
+      <c r="S27" s="1"/>
+    </row>
+    <row r="28" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1">
-        <v>8.3275717539275304E-2</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B28" s="1">
+        <v>6.4781321835991806E-2</v>
+      </c>
+      <c r="C28" s="1">
         <v>1.61983562761508</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D28" s="1">
         <v>1.1200087289977899E-3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E28" s="2">
         <v>-1.70940942511934E-6</v>
       </c>
-      <c r="F3" s="1">
-        <v>2.3942330925430202</v>
-      </c>
-      <c r="G3" s="1">
-        <v>42.104884423720002</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.1493051847343699E-3</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" ht="42.75">
-      <c r="A4" s="1" t="s">
+      <c r="F28" s="1">
+        <v>2.3330316306546202</v>
+      </c>
+      <c r="G28" s="1">
+        <v>41.300474426939402</v>
+      </c>
+      <c r="H28" s="1">
+        <v>7.5220902607897003E-4</v>
+      </c>
+      <c r="S28" s="1"/>
+    </row>
+    <row r="29" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1">
-        <v>8.2647130527365498E-2</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B29" s="1">
+        <v>6.4392626905219894E-2</v>
+      </c>
+      <c r="C29" s="1">
         <v>1.6200414713728299</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D29" s="1">
         <v>6.8440843195613802E-4</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E29" s="2">
         <v>5.4237477020878299E-5</v>
       </c>
-      <c r="F4" s="1">
-        <v>2.3962083117546502</v>
-      </c>
-      <c r="G4" s="1">
-        <v>40.404079591862399</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.00067195361415E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="42.75">
-      <c r="A5" s="1" t="s">
+      <c r="F29" s="1">
+        <v>2.3349682565850598</v>
+      </c>
+      <c r="G29" s="1">
+        <v>40.630893378584197</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1.0436192746553401E-3</v>
+      </c>
+      <c r="S29" s="1"/>
+    </row>
+    <row r="30" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1">
-        <v>8.2574146110371893E-2</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B30" s="1">
+        <v>6.4250407980306304E-2</v>
+      </c>
+      <c r="C30" s="1">
         <v>1.6198594818057499</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D30" s="1">
         <v>6.8108001881204505E-4</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E30" s="2">
         <v>5.4453627681355902E-5</v>
       </c>
-      <c r="F5" s="1">
-        <v>2.39555379468811</v>
-      </c>
-      <c r="G5" s="1">
-        <v>42.340673988065802</v>
-      </c>
-      <c r="H5" s="1">
-        <v>8.1847174767523496E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="42.75">
-      <c r="A6" s="1" t="s">
+      <c r="F30" s="1">
+        <v>2.3343556676952102</v>
+      </c>
+      <c r="G30" s="1">
+        <v>40.4151921543667</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1.0304586414928501E-3</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+    </row>
+    <row r="31" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1">
-        <v>8.23716711721698E-2</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B31" s="1">
+        <v>6.4167196154649705E-2</v>
+      </c>
+      <c r="C31" s="1">
         <v>1.6198443301399199</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D31" s="1">
         <v>7.7481504644868701E-4</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E31" s="2">
         <v>2.8641880118750099E-5</v>
       </c>
-      <c r="F6" s="1">
-        <v>2.3954082023473702</v>
-      </c>
-      <c r="G6" s="1">
-        <v>41.377977264409402</v>
-      </c>
-      <c r="H6" s="1">
-        <v>7.52209587495359E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="42.75">
-      <c r="A7" s="1" t="s">
+      <c r="F31" s="1">
+        <v>2.3342120054478301</v>
+      </c>
+      <c r="G31" s="1">
+        <v>41.377957355055202</v>
+      </c>
+      <c r="H31" s="1">
+        <v>7.5220819468679997E-4</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+    </row>
+    <row r="32" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1">
-        <v>8.2532915515358393E-2</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B32" s="1">
+        <v>6.4208136070914995E-2</v>
+      </c>
+      <c r="C32" s="1">
         <v>1.6197044232872699</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D32" s="1">
         <v>1.1474603762782901E-3</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E32" s="2">
         <v>-1.19834465631219E-5</v>
       </c>
-      <c r="F7" s="1">
-        <v>2.14486622822439</v>
-      </c>
-      <c r="G7" s="1">
-        <v>42.344268627458703</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1.1470673261929801E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="42.75">
-      <c r="A8" s="1" t="s">
+      <c r="F32" s="1">
+        <v>2.0836465602974799</v>
+      </c>
+      <c r="G32" s="1">
+        <v>41.698273446079902</v>
+      </c>
+      <c r="H32" s="1">
+        <v>7.1726100247066101E-4</v>
+      </c>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+    </row>
+    <row r="33" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1">
-        <v>8.2694298166149094E-2</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B33" s="1">
+        <v>6.4378306448205899E-2</v>
+      </c>
+      <c r="C33" s="1">
         <v>1.6198746545175799</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D33" s="1">
         <v>1.0611074307966899E-3</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E33" s="2">
         <v>-7.5088152552855898E-6</v>
       </c>
-      <c r="F8" s="1">
-        <v>2.39569467462043</v>
-      </c>
-      <c r="G8" s="1">
-        <v>42.249490011649499</v>
-      </c>
-      <c r="H8" s="1">
-        <v>6.8106200488620599E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="42.75">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1">
-        <v>8.2653296245640703E-2</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.62350084108952</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1.1208199841096799E-3</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1.15713154860445E-5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2.6487131796863501</v>
-      </c>
-      <c r="G9" s="1">
-        <v>39.793860892501002</v>
-      </c>
-      <c r="H9" s="1">
-        <v>5.7969744964733998E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="42.75">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1">
-        <v>8.3314551683197596E-2</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1.6239805242455601</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1.19211779373671E-3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-1.47392572695851E-5</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2.8564638831557101</v>
-      </c>
-      <c r="G10" s="1">
-        <v>40.789362311009199</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7.5220644759128505E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="42.75">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1">
-        <v>8.3433338441133195E-2</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1.62446194859036</v>
-      </c>
-      <c r="D11" s="1">
-        <v>9.5153340410589096E-4</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2.2974559750219399E-5</v>
-      </c>
-      <c r="F11" s="1">
-        <v>2.6469832230770001</v>
-      </c>
-      <c r="G11" s="1">
-        <v>40.927400699824901</v>
-      </c>
-      <c r="H11" s="1">
-        <v>9.5132643544981103E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="42.75">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1">
-        <v>8.3208643584929701E-2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1.62430809318148</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1.0035122222886101E-3</v>
-      </c>
-      <c r="E12" s="2">
-        <v>4.0243907751170497E-5</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2.6455410129146402</v>
-      </c>
-      <c r="G12" s="1">
-        <v>40.8480529497417</v>
-      </c>
-      <c r="H12" s="1">
-        <v>7.5220768826737795E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="42.75">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1">
-        <v>8.3420473796778499E-2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1.62477629876114</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1.1116336638491301E-3</v>
-      </c>
-      <c r="E13" s="2">
-        <v>-9.9613128905330105E-6</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2.6464111520025102</v>
-      </c>
-      <c r="G13" s="1">
-        <v>39.899003906860202</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1.14591946134388E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="42.75">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1">
-        <v>8.3107161558914899E-2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1.62486422735943</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1.0427331838012901E-3</v>
-      </c>
-      <c r="E14" s="2">
-        <v>8.9550238829479297E-6</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2.6451630354273901</v>
-      </c>
-      <c r="G14" s="1">
-        <v>39.905542744157799</v>
-      </c>
-      <c r="H14" s="1">
-        <v>5.8078143344807295E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="42.75">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1">
-        <v>8.3039185267029303E-2</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1.62564222201577</v>
-      </c>
-      <c r="D15" s="1">
-        <v>8.1502383110239297E-4</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4.0838120759855502E-5</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2.6460120774236602</v>
-      </c>
-      <c r="G15" s="1">
-        <v>40.810961238208897</v>
-      </c>
-      <c r="H15" s="1">
-        <v>6.0900650582167398E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="42.75">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1">
-        <v>8.3538722608662797E-2</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1.62496427111479</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1.2154222328969E-3</v>
-      </c>
-      <c r="E16" s="2">
-        <v>-2.2617714945597699E-5</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2.6463043362485101</v>
-      </c>
-      <c r="G16" s="1">
-        <v>40.941218065706401</v>
-      </c>
-      <c r="H16" s="1">
-        <v>7.5220971621754295E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="42.75">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1">
-        <v>8.3535910062118204E-2</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1.6252221813656</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1.00142273410833E-3</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1.6165173725499801E-5</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2.64585222009006</v>
-      </c>
-      <c r="G17" s="1">
-        <v>40.940933290880203</v>
-      </c>
-      <c r="H17" s="1">
-        <v>7.5220871367623495E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="42.75">
-      <c r="A18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="1">
-        <v>8.3082835466929905E-2</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1.6248694903974701</v>
-      </c>
-      <c r="D18" s="1">
-        <v>6.2295334582414101E-4</v>
-      </c>
-      <c r="E18" s="2">
-        <v>6.6553208117818997E-5</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2.6449795008878501</v>
-      </c>
-      <c r="G18" s="1">
-        <v>41.210784936626098</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5.8657249657950001E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="42.75">
-      <c r="A19" s="1" t="s">
+      <c r="F33" s="1">
+        <v>2.3344754407433301</v>
+      </c>
+      <c r="G33" s="1">
+        <v>41.380931544920301</v>
+      </c>
+      <c r="H33" s="1">
+        <v>7.5221319827744801E-4</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+    </row>
+    <row r="34" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1">
-        <v>8.2670956206444698E-2</v>
-      </c>
-      <c r="C19" s="1">
+      <c r="B34" s="1">
+        <v>6.4317608614747404E-2</v>
+      </c>
+      <c r="C34" s="1">
         <v>1.6200155354838199</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D34" s="1">
         <v>8.1771885358426896E-4</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E34" s="2">
         <v>2.3799624873818999E-5</v>
       </c>
-      <c r="F19" s="1">
-        <v>2.3949581256083499</v>
-      </c>
-      <c r="G19" s="1">
-        <v>42.468990585043002</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1.0175574043783701E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="42.75">
-      <c r="A20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="1">
-        <v>8.22329018284189E-2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.6208958749307201</v>
-      </c>
-      <c r="D20" s="1">
-        <v>6.6126506060004296E-4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4.1305106033644801E-5</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2.1709266461248098</v>
-      </c>
-      <c r="G20" s="1">
-        <v>40.460723470330102</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5.9286624724858201E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="42.75">
-      <c r="A21" s="1" t="s">
+      <c r="F34" s="1">
+        <v>2.3337472515462001</v>
+      </c>
+      <c r="G34" s="1">
+        <v>41.470210330159702</v>
+      </c>
+      <c r="H34" s="1">
+        <v>7.5220786288883804E-4</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+    </row>
+    <row r="35" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="1">
-        <v>8.1803833529134007E-2</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="B35" s="1">
+        <v>6.3677492575877404E-2</v>
+      </c>
+      <c r="C35" s="1">
         <v>1.6212067557749299</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D35" s="1">
         <v>7.1738692684873403E-4</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E35" s="2">
         <v>2.74880154209467E-5</v>
       </c>
-      <c r="F21" s="1">
-        <v>2.3953651756805399</v>
-      </c>
-      <c r="G21" s="1">
-        <v>41.420068766735803</v>
-      </c>
-      <c r="H21" s="1">
-        <v>7.5220697565547595E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="42.75">
-      <c r="A22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="1">
-        <v>8.2226095621156195E-2</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.62000271823762</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1.16571404683784E-3</v>
-      </c>
-      <c r="E22" s="2">
-        <v>-4.22301697655647E-6</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2.3952682079702798</v>
-      </c>
-      <c r="G22" s="1">
-        <v>42.186606476606698</v>
-      </c>
-      <c r="H22" s="1">
-        <v>8.03056382404393E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="42.75">
-      <c r="A23" s="1" t="s">
+      <c r="F35" s="1">
+        <v>2.3341529289798002</v>
+      </c>
+      <c r="G35" s="1">
+        <v>40.842345823164202</v>
+      </c>
+      <c r="H35" s="1">
+        <v>6.4715526168359304E-4</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+    </row>
+    <row r="36" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="1">
-        <v>8.1619568336985804E-2</v>
-      </c>
-      <c r="C23" s="1">
+      <c r="B36" s="1">
+        <v>6.3641331008131394E-2</v>
+      </c>
+      <c r="C36" s="1">
         <v>1.62024450916637</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D36" s="1">
         <v>1.05982624252412E-3</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E36" s="2">
         <v>-1.3529141064933799E-5</v>
       </c>
-      <c r="F23" s="1">
-        <v>2.3956309043518398</v>
-      </c>
-      <c r="G23" s="1">
-        <v>40.294805692967003</v>
-      </c>
-      <c r="H23" s="1">
-        <v>6.6748383189488703E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="42.75">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1">
-        <v>8.3156282475135901E-2</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1.6246517474351401</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1.2832394093051001E-3</v>
-      </c>
-      <c r="E24" s="2">
-        <v>-4.5039025450265098E-5</v>
-      </c>
-      <c r="F24" s="1">
-        <v>2.6451349772380799</v>
-      </c>
-      <c r="G24" s="1">
-        <v>41.462671395556001</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1.1570801635473701E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="42.75">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1">
-        <v>8.3308052923752804E-2</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1.62375786770658</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1.3305457179744299E-3</v>
-      </c>
-      <c r="E25" s="2">
-        <v>-4.00517488312179E-5</v>
-      </c>
-      <c r="F25" s="1">
-        <v>2.89619969520915</v>
-      </c>
-      <c r="G25" s="1">
-        <v>40.593777624199902</v>
-      </c>
-      <c r="H25" s="1">
-        <v>7.5220839565440299E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="42.75">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1">
-        <v>8.3192433829034101E-2</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1.62445657349427</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1.1488949262361599E-3</v>
-      </c>
-      <c r="E26" s="2">
-        <v>-1.3036912286815E-5</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2.6455059000260901</v>
-      </c>
-      <c r="G26" s="1">
-        <v>40.896825551143003</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1.13711272159249E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="42.75">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1">
-        <v>8.3623706474663606E-2</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1.62388373467633</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1.3211340143322401E-3</v>
-      </c>
-      <c r="E27" s="2">
-        <v>-3.4790584613092498E-5</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2.89717815983379</v>
-      </c>
-      <c r="G27" s="1">
-        <v>40.632491852446101</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1.13227516096914E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="42.75">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1">
-        <v>8.3216917778572402E-2</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1.62447539983621</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1.1619972120418399E-3</v>
-      </c>
-      <c r="E28" s="2">
-        <v>-6.8861837271727797E-6</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2.8947230935883499</v>
-      </c>
-      <c r="G28" s="1">
-        <v>40.688720073791103</v>
-      </c>
-      <c r="H28" s="1">
-        <v>7.5220731804934702E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="42.75">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1">
-        <v>8.3221177215463099E-2</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1.6240658175753799</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1.34611239648697E-3</v>
-      </c>
-      <c r="E29" s="2">
-        <v>-3.8973982051738203E-5</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2.8949209914724099</v>
-      </c>
-      <c r="G29" s="1">
-        <v>40.329378683577097</v>
-      </c>
-      <c r="H29" s="1">
-        <v>7.5660709584838897E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="42.75">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1">
-        <v>8.33781973276186E-2</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1.62401974426023</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1.0979108637087199E-3</v>
-      </c>
-      <c r="E30" s="2">
-        <v>6.4089692879704E-6</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2.6452982335850099</v>
-      </c>
-      <c r="G30" s="1">
-        <v>41.214238544996803</v>
-      </c>
-      <c r="H30" s="1">
-        <v>1.08040681674856E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="42.75">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1">
-        <v>8.33668584997104E-2</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1.62396843192504</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1.1956276763198401E-3</v>
-      </c>
-      <c r="E31" s="2">
-        <v>-1.26144128146059E-5</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2.6477043125223498</v>
-      </c>
-      <c r="G31" s="1">
-        <v>40.672324248678201</v>
-      </c>
-      <c r="H31" s="1">
-        <v>5.7862408946219202E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="42.75">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1">
-        <v>8.3201985411368501E-2</v>
-      </c>
-      <c r="C32" s="1">
-        <v>1.62534447696757</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1.0570390030800801E-3</v>
-      </c>
-      <c r="E32" s="2">
-        <v>-3.4741554776058601E-6</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2.3949796634584</v>
-      </c>
-      <c r="G32" s="1">
-        <v>40.941252698427299</v>
-      </c>
-      <c r="H32" s="1">
-        <v>7.5220879266188598E-4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="42.75">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1">
-        <v>8.3110318912883605E-2</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1.6246767088488201</v>
-      </c>
-      <c r="D33" s="1">
-        <v>9.6775230495947499E-4</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1.2811293098655901E-5</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2.6469496727777599</v>
-      </c>
-      <c r="G33" s="1">
-        <v>40.037296507075901</v>
-      </c>
-      <c r="H33" s="1">
-        <v>9.2856514840207905E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="42.75">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1">
-        <v>8.2031859042136696E-2</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1.62117967101831</v>
-      </c>
-      <c r="D34" s="1">
-        <v>7.4081403150172604E-4</v>
-      </c>
-      <c r="E34" s="2">
-        <v>5.6192417281096199E-5</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2.6457261551801898</v>
-      </c>
-      <c r="G34" s="1">
-        <v>39.967050487409502</v>
-      </c>
-      <c r="H34" s="1">
-        <v>5.91413844397934E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="42.75">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1">
-        <v>8.2441921487811098E-2</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1.62085950749531</v>
-      </c>
-      <c r="D35" s="1">
-        <v>7.4047369634396498E-4</v>
-      </c>
-      <c r="E35" s="2">
-        <v>4.5377426729487801E-5</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2.6459057456238302</v>
-      </c>
-      <c r="G35" s="1">
-        <v>41.021281712544699</v>
-      </c>
-      <c r="H35" s="1">
-        <v>7.5220769703127804E-4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="42.75">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1">
-        <v>8.2431599113651E-2</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1.6207551046439601</v>
-      </c>
-      <c r="D36" s="1">
-        <v>4.5136333774447901E-4</v>
-      </c>
-      <c r="E36" s="2">
-        <v>9.1475583453467195E-5</v>
-      </c>
       <c r="F36" s="1">
-        <v>2.6448975819871401</v>
+        <v>2.3344403898874702</v>
       </c>
       <c r="G36" s="1">
-        <v>41.129512935157301</v>
+        <v>41.2813154470877</v>
       </c>
       <c r="H36" s="1">
-        <v>7.5221021777261603E-4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="42.75">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1">
-        <v>8.3008569433927301E-2</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1.62037111978291</v>
-      </c>
-      <c r="D37" s="1">
-        <v>9.3384052361766595E-4</v>
-      </c>
-      <c r="E37" s="2">
-        <v>1.56159530632519E-5</v>
-      </c>
-      <c r="F37" s="1">
-        <v>2.3956082969512398</v>
-      </c>
-      <c r="G37" s="1">
-        <v>41.202154939667999</v>
-      </c>
-      <c r="H37" s="1">
-        <v>7.5220882716310296E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="42.75">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1">
-        <v>8.2766374795728306E-2</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1.6201546919669101</v>
-      </c>
-      <c r="D38" s="1">
-        <v>9.0910924833357903E-4</v>
-      </c>
-      <c r="E38" s="2">
-        <v>1.70131664205842E-5</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2.3957416806344698</v>
-      </c>
-      <c r="G38" s="1">
-        <v>41.978791003323103</v>
-      </c>
-      <c r="H38" s="1">
-        <v>1.09810641610964E-3</v>
-      </c>
+        <v>7.5220862507029899E-4</v>
+      </c>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2493,13 +2585,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.875" customWidth="1"/>
+    <col min="1" max="1" width="27.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2509,8 +2601,10 @@
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -2518,7 +2612,7 @@
         <v>4.0504847360743401</v>
       </c>
       <c r="C2" s="1">
-        <v>8.3156282475135901E-2</v>
+        <v>6.4664938143317294E-2</v>
       </c>
       <c r="F2">
         <v>894</v>
@@ -2526,8 +2620,10 @@
       <c r="G2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -2535,7 +2631,7 @@
         <v>4.0496768121653703</v>
       </c>
       <c r="C3" s="1">
-        <v>8.3308052923752804E-2</v>
+        <v>6.48925563524336E-2</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -2546,10 +2642,12 @@
       </c>
       <c r="G3">
         <f>AVERAGE(C2:C36)</f>
-        <v>8.2936270811090188E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>6.4567503279549049E-2</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
@@ -2557,7 +2655,7 @@
         <v>4.0401570007949097</v>
       </c>
       <c r="C4" s="1">
-        <v>8.3192433829034101E-2</v>
+        <v>6.4717624366303003E-2</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -2568,10 +2666,12 @@
       </c>
       <c r="G4">
         <f>_xlfn.STDEV.S(C2:C36)</f>
-        <v>4.9284213581769548E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>3.7162056188217856E-4</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -2579,7 +2679,7 @@
         <v>4.0452933053436704</v>
       </c>
       <c r="C5" s="1">
-        <v>8.3623706474663606E-2</v>
+        <v>6.5096945322289101E-2</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -2590,10 +2690,12 @@
       </c>
       <c r="G5">
         <f>G4/G3/SQRT(COUNT(C2:C37))</f>
-        <v>1.0044522714183018E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>9.7286307528265557E-4</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -2601,10 +2703,12 @@
         <v>4.0393053513377497</v>
       </c>
       <c r="C6" s="1">
-        <v>8.3216917778572402E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>6.4780635694392893E-2</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -2612,10 +2716,12 @@
         <v>4.0427869051265404</v>
       </c>
       <c r="C7" s="1">
-        <v>8.3221177215463099E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>6.4828747039054904E-2</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -2623,10 +2729,12 @@
         <v>4.0371132630075302</v>
       </c>
       <c r="C8" s="1">
-        <v>8.33781973276186E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>6.4845896931015903E-2</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -2634,10 +2742,12 @@
         <v>4.0301105995964903</v>
       </c>
       <c r="C9" s="1">
-        <v>8.33668584997104E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>6.4898532838035997E-2</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2645,10 +2755,12 @@
         <v>4.0520999190004696</v>
       </c>
       <c r="C10" s="1">
-        <v>8.2653296245640703E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>6.4393394651674596E-2</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2656,10 +2768,12 @@
         <v>4.0532303423785203</v>
       </c>
       <c r="C11" s="1">
-        <v>8.3314551683197596E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>6.4836933722996301E-2</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -2667,10 +2781,12 @@
         <v>4.0597656945719098</v>
       </c>
       <c r="C12" s="1">
-        <v>8.3433338441133195E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>6.4898123293677099E-2</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -2678,10 +2794,12 @@
         <v>4.0397313521665303</v>
       </c>
       <c r="C13" s="1">
-        <v>8.3208643584929701E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>6.48141939607636E-2</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -2689,10 +2807,12 @@
         <v>4.0389446603470498</v>
       </c>
       <c r="C14" s="1">
-        <v>8.3420473796778499E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>6.4945690313312696E-2</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -2700,10 +2820,12 @@
         <v>4.0491521884945199</v>
       </c>
       <c r="C15" s="1">
-        <v>8.3107161558914899E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>6.4750632359324503E-2</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -2711,10 +2833,12 @@
         <v>4.0282207799584802</v>
       </c>
       <c r="C16" s="1">
-        <v>8.3039185267029303E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>6.46466961945657E-2</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -2722,10 +2846,12 @@
         <v>4.0373666399902799</v>
       </c>
       <c r="C17" s="1">
-        <v>8.3538722608662797E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>6.5070391277710998E-2</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -2733,10 +2859,12 @@
         <v>4.0254616281370303</v>
       </c>
       <c r="C18" s="1">
-        <v>8.3535910062118204E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>6.5003508402351404E-2</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -2744,10 +2872,12 @@
         <v>4.0346044905874798</v>
       </c>
       <c r="C19" s="1">
-        <v>8.3082835466929905E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>6.4702157939462199E-2</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -2755,10 +2885,12 @@
         <v>4.0220126763814203</v>
       </c>
       <c r="C20" s="1">
-        <v>8.3201985411368501E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>6.4789520162763903E-2</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -2766,10 +2898,12 @@
         <v>4.0377589881580498</v>
       </c>
       <c r="C21" s="1">
-        <v>8.3110318912883605E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>6.4698100702121605E-2</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2777,10 +2911,12 @@
         <v>4.0016969711271004</v>
       </c>
       <c r="C22" s="1">
-        <v>8.2031859042136696E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>6.39060983563466E-2</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -2788,10 +2924,12 @@
         <v>3.9850777599500198</v>
       </c>
       <c r="C23" s="1">
-        <v>8.2441921487811098E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>6.4217223623450101E-2</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
@@ -2799,10 +2937,12 @@
         <v>4.0132441168710704</v>
       </c>
       <c r="C24" s="1">
-        <v>8.2431599113651E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>6.4146735969449406E-2</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
@@ -2810,10 +2950,12 @@
         <v>4.0107044449171996</v>
       </c>
       <c r="C25" s="1">
-        <v>8.3008569433927301E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>6.4629796704458606E-2</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>45</v>
       </c>
@@ -2821,10 +2963,12 @@
         <v>4.0042080560711302</v>
       </c>
       <c r="C26" s="1">
-        <v>8.2766374795728306E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>6.43943878164248E-2</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
@@ -2832,10 +2976,12 @@
         <v>4.0137738076926297</v>
       </c>
       <c r="C27" s="1">
-        <v>8.2788867848109599E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>6.4478725052475205E-2</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>12</v>
       </c>
@@ -2843,10 +2989,12 @@
         <v>4.0189067438591497</v>
       </c>
       <c r="C28" s="1">
-        <v>8.3275717539275304E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>6.4781321835991806E-2</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -2854,10 +3002,12 @@
         <v>4.0019418304313801</v>
       </c>
       <c r="C29" s="1">
-        <v>8.2647130527365498E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>6.4392626905219894E-2</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
@@ -2865,10 +3015,12 @@
         <v>4.0058057955871602</v>
       </c>
       <c r="C30" s="1">
-        <v>8.2574146110371893E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>6.4250407980306304E-2</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
@@ -2876,10 +3028,12 @@
         <v>4.0060301681826802</v>
       </c>
       <c r="C31" s="1">
-        <v>8.23716711721698E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>6.4167196154649705E-2</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
@@ -2887,10 +3041,12 @@
         <v>3.99829105994908</v>
       </c>
       <c r="C32" s="1">
-        <v>8.2532915515358393E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>6.4208136070914995E-2</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
@@ -2898,10 +3054,12 @@
         <v>3.9906830558389799</v>
       </c>
       <c r="C33" s="1">
-        <v>8.2694298166149094E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>6.4378306448205899E-2</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2909,10 +3067,12 @@
         <v>3.99736506566357</v>
       </c>
       <c r="C34" s="1">
-        <v>8.2670956206444698E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>6.4317608614747404E-2</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>29</v>
       </c>
@@ -2920,10 +3080,12 @@
         <v>3.98390122498571</v>
       </c>
       <c r="C35" s="1">
-        <v>8.1803833529134007E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>6.3677492575877404E-2</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
@@ -2931,8 +3093,22 @@
         <v>3.9792620371784699</v>
       </c>
       <c r="C36" s="1">
-        <v>8.1619568336985804E-2</v>
-      </c>
+        <v>6.3641331008131394E-2</v>
+      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C39" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
